--- a/Outputs/Scenarios/PtX_demand_IT_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IT_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004194814982415169</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01392222928044055</v>
+        <v>0.0169556770774016</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02320371546740091</v>
+        <v>0.02061622770018015</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>6.044018326571965e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.009281486186960364</v>
+        <v>0.008835526157220065</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006209912877846326</v>
       </c>
       <c r="K30" t="n">
-        <v>0.07452042060758937</v>
+        <v>0.09075731781472617</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1242007010126489</v>
+        <v>0.1103508589474002</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0003268375198866488</v>
       </c>
       <c r="K42" t="n">
-        <v>0.04968028040505958</v>
+        <v>0.04729322526317152</v>
       </c>
     </row>
     <row r="43">
